--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Francine attend encore. Puis la maîtresse dit : Francine, c'est ton tour. Francine parle. Elle dit : le nuage est blanc. La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour. Elle dit : j'aime ce livre. Le soir, maman demande. Francine dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
+          <t>Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Francine attend encore. Puis Francine, c'est ton tour. Francine parle. Le nuage est blanc. La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour. J'aime ce livre. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Francine attend encore. Puis
+maitresse|Francine, c'est ton tour.
+narrateur|Francine parle.
+narrateur|Le nuage est blanc.
+narrateur|La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour.
+narrateur|J'aime ce livre.
+narrateur|Le soir, maman demande.
+enfant-f|J'ai levé la main. J'ai su attendre.
+narrateur|Puis parler, c'était mon tour.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Francine veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Francine a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Francine range son cartable. Maman l'attend à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Puis parler, c'était mon tour.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Francine veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Francine a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Francine range son cartable. Maman l'attend à la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Francine attend puis parle</t>
+          <t>Le chemin d'escargot de Sarah</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COL.POL.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'écharpe de laine chatouille la joue. Sarah voit le chemin d'escargot sur la vitre. Elle lève la main. Elle attend. Puis elle parle, au tapis et aux livres.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Francine attend encore. Puis Francine, c'est ton tour. Francine parle. Le nuage est blanc. La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour. J'aime ce livre. Le soir, maman demande. J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.</t>
+          <t>Le radiateur de l'entrée fait tic, tic, tic. L'écharpe de laine chatouille la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la vitre de la classe, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. Bravo. La classe sent les crayons et le lait tiède. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. La traînée d'escargot brille encore un peu. Bonjour les enfants. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot a laissé un chemin d'argent. Elle lève la main. Elle attend. Un camarade parle d'abord d'un ver de terre. Sarah attend encore, la main haute. Elle regarde la vitre, tout doucement. Sarah, c'est ton tour. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la vitre. Merci, Sarah. Tu as attendu. Puis tu as parlé. C'est du bon travail. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est ton tour, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Tu as attendu. Puis parler, c'était ton tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1329,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut attendre. Un camarade parle d'abord. Francine attend encore. Puis
-maitresse|Francine, c'est ton tour.
-narrateur|Francine parle.
-narrateur|Le nuage est blanc.
-narrateur|La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour.
-narrateur|J'aime ce livre.
-narrateur|Le soir, maman demande.
-enfant-f|J'ai levé la main. J'ai su attendre.
-narrateur|Puis parler, c'était mon tour.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le radiateur de l'entrée fait tic, tic, tic.
+narrateur|L'écharpe de laine chatouille la joue de Sarah.
+narrateur|Elle sent le savon de maman.
+maman|L'écharpe, un tour. Pas trop serré.
+papa|Tes gants sont dans la poche. Tu les sens ?
+enfant-f|Oui. Ils sont tout doux.
+narrateur|Dehors, l'air est frais et calme.
+narrateur|Sur la vitre de la classe, une traînée brillante.
+narrateur|Un escargot est passé, tout lentement.
+papa|Tu as vu le petit chemin luisant ?
+enfant-f|Il brille.
+maman|Au revoir, Sarah. On revient.
+enfant-f|Au revoir, maman.
+papa|Tu poses l'écharpe au crochet. Bravo.
+narrateur|La classe sent les crayons et le lait tiède.
+narrateur|En ce moment, Sarah s'assoit près de la fenêtre.
+narrateur|Elle pose les mains sur ses genoux.
+narrateur|La traînée d'escargot brille encore un peu.
+maitresse|Bonjour les enfants.
+enfant-f|Bonjour.
+maitresse|Qui a vu un petit animal tout lent ?
+narrateur|Sarah a une idée.
+narrateur|L'escargot a laissé un chemin d'argent.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+narrateur|Un camarade parle d'abord d'un ver de terre.
+narrateur|Sarah attend encore, la main haute.
+narrateur|Elle regarde la vitre, tout doucement.
+maitresse|Sarah, c'est ton tour.
+maitresse|Tu peux parler.
+enfant-f|L'escargot a laissé un chemin.
+enfant-f|Il brille sur la vitre.
+maitresse|Merci, Sarah. Tu as attendu. Puis tu as parlé.
+maitresse|C'est du bon travail.
+narrateur|Plus tard, au coin des livres, un banc de bois attend.
+narrateur|Sarah ouvre un album aux pages épaisses.
+narrateur|Elle a encore une idée.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maitresse|Sarah, c'est ton tour, ici aussi.
+enfant-f|J'aime ce livre.
+enfant-f|Il y a un escargot, tout lent.
+maitresse|Tu as attendu. Puis parler, c'était ton tour.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>radiateur,pages</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Francine veut parler. Que fait-elle d'abord ?</t>
+          <t>Sarah veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1559,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Francine veut parler. Que fait-elle d'abord ?</t>
+          <t>narrateur|Sarah veut parler.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Francine a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres.</t>
+          <t>Sarah a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres. Tu as levé la main. Bravo. Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1732,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Francine a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres.</t>
+          <t>narrateur|Sarah a levé la main.
+narrateur|Elle a attendu.
+narrateur|Puis parler, c'était son tour.
+narrateur|Au tapis, puis aux livres.
+maitresse|Tu as levé la main. Bravo.
+maitresse|Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Francine range son cartable. Maman l'attend à la porte.</t>
+          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. Maman attend près de la porte. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé de l'escargot ? Oui. Et du livre, aussi. Bravo, Sarah. Tu as fait du bon travail. On rentre. Le radiateur fera tic, tic. Le soir, l'écharpe sèche près du radiateur. La vitre de la maison est propre et calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1901,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Francine range son cartable. Maman l'attend à la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Plus tard, Sarah range son cartable.
+narrateur|L'écharpe de laine est encore au crochet.
+narrateur|Maman attend près de la porte.
+maman|Tu as passé un bon moment ?
+enfant-f|J'ai levé la main.
+enfant-f|J'ai su attendre.
+enfant-f|Puis parler, c'était mon tour.
+papa|Tu as parlé de l'escargot ?
+enfant-f|Oui. Et du livre, aussi.
+maman|Bravo, Sarah. Tu as fait du bon travail.
+papa|On rentre. Le radiateur fera tic, tic.
+narrateur|Le soir, l'écharpe sèche près du radiateur.
+narrateur|La vitre de la maison est propre et calme.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>radiateur,pas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le radiateur chante tout bas. Tu as attendu. Puis tu as parlé. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2085,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le radiateur chante tout bas.
+papa|Tu as attendu. Puis tu as parlé.
+maman|Bonne soirée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -1332,17 +1332,22 @@
           <t>narrateur|Le radiateur de l'entrée fait tic, tic, tic.
 narrateur|L'écharpe de laine chatouille la joue de Sarah.
 narrateur|Elle sent le savon de maman.
-maman|L'écharpe, un tour. Pas trop serré.
-papa|Tes gants sont dans la poche. Tu les sens ?
-enfant-f|Oui. Ils sont tout doux.
+maman|L'écharpe, un tour.
+maman|Pas trop serré.
+papa|Tes gants sont dans la poche.
+papa|Tu les sens ?
+enfant-f|Oui.
+enfant-f|Ils sont tout doux.
 narrateur|Dehors, l'air est frais et calme.
 narrateur|Sur la vitre de la classe, une traînée brillante.
 narrateur|Un escargot est passé, tout lentement.
 papa|Tu as vu le petit chemin luisant ?
 enfant-f|Il brille.
-maman|Au revoir, Sarah. On revient.
+maman|Au revoir, Sarah.
+maman|On revient.
 enfant-f|Au revoir, maman.
-papa|Tu poses l'écharpe au crochet. Bravo.
+papa|Tu poses l'écharpe au crochet.
+papa|Bravo.
 narrateur|La classe sent les crayons et le lait tiède.
 narrateur|En ce moment, Sarah s'assoit près de la fenêtre.
 narrateur|Elle pose les mains sur ses genoux.
@@ -1361,7 +1366,9 @@
 maitresse|Tu peux parler.
 enfant-f|L'escargot a laissé un chemin.
 enfant-f|Il brille sur la vitre.
-maitresse|Merci, Sarah. Tu as attendu. Puis tu as parlé.
+maitresse|Merci, Sarah.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.
 maitresse|C'est du bon travail.
 narrateur|Plus tard, au coin des livres, un banc de bois attend.
 narrateur|Sarah ouvre un album aux pages épaisses.
@@ -1371,7 +1378,8 @@
 maitresse|Sarah, c'est ton tour, ici aussi.
 enfant-f|J'aime ce livre.
 enfant-f|Il y a un escargot, tout lent.
-maitresse|Tu as attendu. Puis parler, c'était ton tour.</t>
+maitresse|Tu as attendu.
+maitresse|Puis parler, c'était ton tour.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1736,8 +1744,10 @@
 narrateur|Elle a attendu.
 narrateur|Puis parler, c'était son tour.
 narrateur|Au tapis, puis aux livres.
-maitresse|Tu as levé la main. Bravo.
-maitresse|Tu as attendu. Puis tu as parlé.</t>
+maitresse|Tu as levé la main.
+maitresse|Bravo.
+maitresse|Tu as attendu.
+maitresse|Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1765,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. Maman attend près de la porte. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé de l'escargot ? Oui. Et du livre, aussi. Bravo, Sarah. Tu as fait du bon travail. On rentre. Le radiateur fera tic, tic. Le soir, l'écharpe sèche près du radiateur. La vitre de la maison est propre et calme.</t>
+          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé de l'escargot ? Oui. Et du livre, aussi. Bravo, Sarah. Tu as fait du bon travail. On rentre. Le radiateur fera tic, tic. Le soir, l'écharpe sèche près du radiateur. La vitre de la maison est propre et calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1903,15 +1913,18 @@
         <is>
           <t>narrateur|Plus tard, Sarah range son cartable.
 narrateur|L'écharpe de laine est encore au crochet.
-narrateur|Maman attend près de la porte.
+narrateur|La porte s'ouvre.
 maman|Tu as passé un bon moment ?
 enfant-f|J'ai levé la main.
 enfant-f|J'ai su attendre.
 enfant-f|Puis parler, c'était mon tour.
 papa|Tu as parlé de l'escargot ?
-enfant-f|Oui. Et du livre, aussi.
-maman|Bravo, Sarah. Tu as fait du bon travail.
-papa|On rentre. Le radiateur fera tic, tic.
+enfant-f|Oui.
+enfant-f|Et du livre, aussi.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+papa|On rentre.
+papa|Le radiateur fera tic, tic.
 narrateur|Le soir, l'écharpe sèche près du radiateur.
 narrateur|La vitre de la maison est propre et calme.</t>
         </is>
@@ -2086,7 +2099,8 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Le radiateur chante tout bas.
-papa|Tu as attendu. Puis tu as parlé.
+papa|Tu as attendu.
+papa|Puis tu as parlé.
 maman|Bonne soirée, ma grande.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2110,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2167,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le chemin d'escargot de Sarah</t>
+          <t>Le chemin d'argent de Sarah</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>classe, tapis puis coins livres</t>
+          <t>allée, classe, coin des livres</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Francine, maman, maîtresse</t>
+          <t>Sarah, papa, maman, maîtresse</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L'écharpe de laine chatouille la joue. Sarah voit le chemin d'escargot sur la vitre. Elle lève la main. Elle attend. Puis elle parle, au tapis et aux livres.</t>
+          <t>Sarah veut raconter le chemin d'escargot sur la boîte aux lettres, puis le livre. Elle lève la main, elle attend, puis elle parle.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur de l'entrée fait tic, tic, tic. L'écharpe de laine chatouille la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la vitre de la classe, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. Bravo. La classe sent les crayons et le lait tiède. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. La traînée d'escargot brille encore un peu. Bonjour les enfants. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot a laissé un chemin d'argent. Elle lève la main. Elle attend. Un camarade parle d'abord d'un ver de terre. Sarah attend encore, la main haute. Elle regarde la vitre, tout doucement. Sarah, c'est ton tour. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la vitre. Merci, Sarah. Tu as attendu. Puis tu as parlé. C'est du bon travail. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est ton tour, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Tu as attendu. Puis parler, c'était ton tour.</t>
+          <t>Un bouton de laine pend au manteau. Il tient par un seul fil, tout fin. L'écharpe chatouille encore la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la boîte aux lettres, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Comme un fil d'argent. Tu pourras le raconter. Le chemin sent l'herbe coupée. La classe sent les crayons et le lait tiède. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Une autre traînée brille un peu sur la vitre. Bonjour. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot de la boîte aux lettres. Le chemin d'argent. Le mot est déjà là. Elle avance un peu sur sa chaise. La maîtresse range encore des crayons dans un pot. Le pot fait un petit bruit de bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Francine attend encore. Puis la maîtresse dit : Francine, c'est ton tour. Francine parle. Elle dit : le nuage est blanc. La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour. Elle dit : j'aime ce livre. Le soir, maman demande. Francine dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un bouton de laine pend au manteau. Il tient par un seul fil, tout fin. L'écharpe chatouille encore la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la boîte aux lettres, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Comme un fil d'argent. Tu pourras le raconter. Le chemin sent l'herbe coupée. La classe sent les crayons et le lait tiède. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Une autre traînée brille un peu sur la vitre. Bonjour. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot de la boîte aux lettres. Le chemin d'argent. Le mot est déjà là. Elle avance un peu sur sa chaise. La maîtresse range encore des crayons dans un pot. Le pot fait un petit bruit de bois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,8 +1329,9 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le radiateur de l'entrée fait tic, tic, tic.
-narrateur|L'écharpe de laine chatouille la joue de Sarah.
+          <t>narrateur|Un bouton de laine pend au manteau.
+narrateur|Il tient par un seul fil, tout fin.
+narrateur|L'écharpe chatouille encore la joue de Sarah.
 narrateur|Elle sent le savon de maman.
 maman|L'écharpe, un tour.
 maman|Pas trop serré.
@@ -1339,52 +1340,36 @@
 enfant-f|Oui.
 enfant-f|Ils sont tout doux.
 narrateur|Dehors, l'air est frais et calme.
-narrateur|Sur la vitre de la classe, une traînée brillante.
+narrateur|Sur la boîte aux lettres, une traînée brillante.
 narrateur|Un escargot est passé, tout lentement.
 papa|Tu as vu le petit chemin luisant ?
 enfant-f|Il brille.
+enfant-f|Comme un fil d'argent.
+maman|Tu pourras le raconter.
+narrateur|Le chemin sent l'herbe coupée.
+narrateur|La classe sent les crayons et le lait tiède.
 maman|Au revoir, Sarah.
 maman|On revient.
 enfant-f|Au revoir, maman.
 papa|Tu poses l'écharpe au crochet.
-papa|Bravo.
-narrateur|La classe sent les crayons et le lait tiède.
 narrateur|En ce moment, Sarah s'assoit près de la fenêtre.
 narrateur|Elle pose les mains sur ses genoux.
-narrateur|La traînée d'escargot brille encore un peu.
-maitresse|Bonjour les enfants.
+narrateur|Une autre traînée brille un peu sur la vitre.
+maitresse|Bonjour.
 enfant-f|Bonjour.
 maitresse|Qui a vu un petit animal tout lent ?
 narrateur|Sarah a une idée.
-narrateur|L'escargot a laissé un chemin d'argent.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-narrateur|Un camarade parle d'abord d'un ver de terre.
-narrateur|Sarah attend encore, la main haute.
-narrateur|Elle regarde la vitre, tout doucement.
-maitresse|Sarah, c'est ton tour.
-maitresse|Tu peux parler.
-enfant-f|L'escargot a laissé un chemin.
-enfant-f|Il brille sur la vitre.
-maitresse|Merci, Sarah.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.
-maitresse|C'est du bon travail.
-narrateur|Plus tard, au coin des livres, un banc de bois attend.
-narrateur|Sarah ouvre un album aux pages épaisses.
-narrateur|Elle a encore une idée.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-maitresse|Sarah, c'est ton tour, ici aussi.
-enfant-f|J'aime ce livre.
-enfant-f|Il y a un escargot, tout lent.
-maitresse|Tu as attendu.
-maitresse|Puis parler, c'était ton tour.</t>
+narrateur|L'escargot de la boîte aux lettres.
+narrateur|Le chemin d'argent.
+narrateur|Le mot est déjà là.
+narrateur|Elle avance un peu sur sa chaise.
+narrateur|La maîtresse range encore des crayons dans un pot.
+narrateur|Le pot fait un petit bruit de bois.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>radiateur,pages</t>
+          <t>pas</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Francine veut parler. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1446,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle lève la main et elle attend. Que fait Francine ?</t>
+          <t>Elle lève la main et elle attend. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1571,7 +1556,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a levé la main. Elle a attendu. Puis parler, c'était son tour. Au tapis, puis aux livres. Tu as levé la main. Bravo. Tu as attendu. Puis tu as parlé.</t>
+          <t>Sarah lève la main. Elle attend, la main haute. Elle regarde la vitre, tout doucement. Sa main ne descend pas. Sarah, c'est toi. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la boîte aux lettres. Comme un fil d'argent. Un chemin d'argent, oui. Il allait tout lentement. Merci, Sarah. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Il y a un escargot, tout lent, sur une feuille. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est toi, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Comme celui de la boîte. Comme celui de la boîte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Francine a levé la main. Elle a attendu. &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; parler, c'était son tour. Au tapis, puis aux livres.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah lève la main. Elle attend, la main haute. Elle regarde la vitre, tout doucement. Sa main ne descend pas. Sarah, c'est toi. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la boîte aux lettres. Comme un fil d'argent. Un chemin d'argent, oui. Il allait tout lentement. Merci, Sarah. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Il y a un escargot, tout lent, sur une feuille. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est toi, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Comme celui de la boîte. Comme celui de la boîte.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,17 +1724,36 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a levé la main.
-narrateur|Elle a attendu.
-narrateur|Puis parler, c'était son tour.
-narrateur|Au tapis, puis aux livres.
-maitresse|Tu as levé la main.
-maitresse|Bravo.
-maitresse|Tu as attendu.
-maitresse|Puis tu as parlé.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah lève la main.
+narrateur|Elle attend, la main haute.
+narrateur|Elle regarde la vitre, tout doucement.
+narrateur|Sa main ne descend pas.
+maitresse|Sarah, c'est toi.
+maitresse|Tu peux parler.
+enfant-f|L'escargot a laissé un chemin.
+enfant-f|Il brille sur la boîte aux lettres.
+enfant-f|Comme un fil d'argent.
+maitresse|Un chemin d'argent, oui.
+enfant-f|Il allait tout lentement.
+maitresse|Merci, Sarah.
+narrateur|Plus tard, au coin des livres, un banc de bois attend.
+narrateur|Sarah ouvre un album aux pages épaisses.
+narrateur|Il y a un escargot, tout lent, sur une feuille.
+narrateur|Elle a encore une idée.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+maitresse|Sarah, c'est toi, ici aussi.
+enfant-f|J'aime ce livre.
+enfant-f|Il y a un escargot, tout lent.
+maitresse|Comme celui de la boîte.
+enfant-f|Comme celui de la boîte.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. Tu as parlé de l'escargot ? Oui. Et du livre, aussi. Bravo, Sarah. Tu as fait du bon travail. On rentre. Le radiateur fera tic, tic. Le soir, l'écharpe sèche près du radiateur. La vitre de la maison est propre et calme.</t>
+          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai parlé de l'escargot. Et du livre, aussi. Le chemin d'argent ? Oui. Sur la boîte aux lettres. On rentre. Le bouton tient encore, tout juste. Le soir, l'écharpe sèche près du radiateur. Sarah regarde la boîte aux lettres, par la porte. Le chemin est encore un peu là. Un peu, oui. Demain, il sera peut-être parti. Sarah touche le fil du bouton. On le recoud tout à l'heure. Le livre aussi avait un escargot. Tout lent, comme le vrai.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Francine range son cartable. Maman l'attend à la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai parlé de l'escargot. Et du livre, aussi. Le chemin d'argent ? Oui. Sur la boîte aux lettres. On rentre. Le bouton tient encore, tout juste. Le soir, l'écharpe sèche près du radiateur. Sarah regarde la boîte aux lettres, par la porte. Le chemin est encore un peu là. Un peu, oui. Demain, il sera peut-être parti. Sarah touche le fil du bouton. On le recoud tout à l'heure. Le livre aussi avait un escargot. Tout lent, comme le vrai.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1915,23 +1918,27 @@
 narrateur|L'écharpe de laine est encore au crochet.
 narrateur|La porte s'ouvre.
 maman|Tu as passé un bon moment ?
-enfant-f|J'ai levé la main.
-enfant-f|J'ai su attendre.
-enfant-f|Puis parler, c'était mon tour.
-papa|Tu as parlé de l'escargot ?
+enfant-f|J'ai parlé de l'escargot.
+enfant-f|Et du livre, aussi.
+papa|Le chemin d'argent ?
 enfant-f|Oui.
-enfant-f|Et du livre, aussi.
-maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-papa|On rentre.
-papa|Le radiateur fera tic, tic.
+enfant-f|Sur la boîte aux lettres.
+maman|On rentre.
+papa|Le bouton tient encore, tout juste.
 narrateur|Le soir, l'écharpe sèche près du radiateur.
-narrateur|La vitre de la maison est propre et calme.</t>
+narrateur|Sarah regarde la boîte aux lettres, par la porte.
+enfant-f|Le chemin est encore un peu là.
+maman|Un peu, oui.
+papa|Demain, il sera peut-être parti.
+narrateur|Sarah touche le fil du bouton.
+maman|On le recoud tout à l'heure.
+enfant-f|Le livre aussi avait un escargot.
+papa|Tout lent, comme le vrai.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>radiateur,pas</t>
+          <t>pas</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur chante tout bas. Tu as attendu. Puis tu as parlé. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,14 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le radiateur chante tout bas.
-papa|Tu as attendu.
-papa|Puis tu as parlé.
+          <t>narrateur|Le bouton de laine ne pend plus.
+papa|Le chemin était d'argent.
 maman|Bonne soirée, ma grande.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2197,6 +2202,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande. L'histoire est finie.</t>
+          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,8 +2107,7 @@
         <is>
           <t>narrateur|Le bouton de laine ne pend plus.
 papa|Le chemin était d'argent.
-maman|Bonne soirée, ma grande.
-narrateur|L'histoire est finie.</t>
+maman|Bonne soirée, ma grande.</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2207,6 +2206,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.002-11.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.002-11.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le chemin d'argent de Sarah</t>
+          <t>Le chemin d'escargot de Sarah</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>allée, classe, coin des livres</t>
+          <t>entrée au radiateur, classe, tapis, coin des livres</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sarah, papa, maman, maîtresse</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut raconter le chemin d'escargot sur la boîte aux lettres, puis le livre. Elle lève la main, elle attend, puis elle parle.</t>
+          <t>Un chemin d'argent court sur la vitre. Sur le chemin, un éclat d'escargot brille. Sarah veut le dire, maintenant. Elle coupe papa : les mots se perdent. À la classe, elle ouvre la bouche trop tôt. Elle refuse de foncer, lève la main, attend, parle. Merci vécu. L'éclat d'escargot tient sur la vitre.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un bouton de laine pend au manteau. Il tient par un seul fil, tout fin. L'écharpe chatouille encore la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la boîte aux lettres, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Comme un fil d'argent. Tu pourras le raconter. Le chemin sent l'herbe coupée. La classe sent les crayons et le lait tiède. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Une autre traînée brille un peu sur la vitre. Bonjour. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot de la boîte aux lettres. Le chemin d'argent. Le mot est déjà là. Elle avance un peu sur sa chaise. La maîtresse range encore des crayons dans un pot. Le pot fait un petit bruit de bois.</t>
+          <t>Un chemin d'argent court sur la vitre. Il est mince, un peu luisant. L'air sent le savon de maman. L'écharpe de laine chatouille la joue de Sarah. Elle pique un peu, maman. C'est la laine, près du cou. Le radiateur de l'entrée fait tic. Tu l'entends, Sarah ? Oui, papa. Il chante, près de nous. Sarah connaît cette entrée. Ce chemin, lui, est nouveau. Sur la vitre, un éclat d'escargot brille. Il est petit, papa. C'est le soleil sur le chemin. Un escargot est passé ! Tu as vu le petit chemin luisant ? Il brille. Je veux le dire, maintenant ! Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont chauds. Dehors, l'air est frais. La vitre est froide sous le doigt. Elle est lisse, papa. Maman tourne l'écharpe, un tour. Pas trop serré. D'accord, maman. Papa parle près du crochet. L'écharpe, au crochet, Sarah. Les mots de Sarah se cognent aux siens. Personne ne tourne la tête. Papa, le chemin ! Tu disais quelque chose, Sarah ? Le chemin d'argent. Le sourire de Sarah disparaît. L'éclat d'escargot tremble, puis tient. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne sort pas, maman. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux raconter le chemin ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. Au revoir, Sarah. Au revoir, maman. On revient te chercher. Au revoir, papa. En ce moment, Sarah entre dans la classe. La classe sent les crayons et le lait tiède. Sarah pose l'écharpe au crochet. Le tapis est un peu froid, sous les genoux. Elle s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Le chemin d'argent reste sur la vitre. La maîtresse parle près du tapis. Une affiche montre un animal lent. Sarah a une idée. Le chemin d'escargot brille, près d'elle. Je veux parler du chemin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un bouton de laine pend au manteau. Il tient par un seul fil, tout fin. L'écharpe chatouille encore la joue de Sarah. Elle sent le savon de maman. L'écharpe, un tour. Pas trop serré. Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont tout doux. Dehors, l'air est frais et calme. Sur la boîte aux lettres, une traînée brillante. Un escargot est passé, tout lentement. Tu as vu le petit chemin luisant ? Il brille. Comme un fil d'argent. Tu pourras le raconter. Le chemin sent l'herbe coupée. La classe sent les crayons et le lait tiède. Au revoir, Sarah. On revient. Au revoir, maman. Tu poses l'écharpe au crochet. En ce moment, Sarah s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Une autre traînée brille un peu sur la vitre. Bonjour. Bonjour. Qui a vu un petit animal tout lent ? Sarah a une idée. L'escargot de la boîte aux lettres. Le chemin d'argent. Le mot est déjà là. Elle avance un peu sur sa chaise. La maîtresse range encore des crayons dans un pot. Le pot fait un petit bruit de bois.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un chemin d'argent court sur la vitre. Il est mince, un peu luisant. L'air sent le savon de maman. L'écharpe de laine chatouille la joue de Sarah. Elle pique un peu, maman. C'est la laine, près du cou. Le radiateur de l'entrée fait tic. Tu l'entends, Sarah ? Oui, papa. Il chante, près de nous. Sarah connaît cette entrée. Ce chemin, lui, est nouveau. Sur la vitre, un &lt;emphasis level="moderate"&gt;éclat d'escargot&lt;/emphasis&gt; brille. Il est petit, papa. C'est le soleil sur le chemin. Un escargot est passé ! Tu as vu le petit chemin luisant ? Il brille. Je veux le dire, maintenant ! Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont chauds. Dehors, l'air est frais. La vitre est froide sous le doigt. Elle est lisse, papa. Maman tourne l'écharpe, un tour. Pas trop serré. D'accord, maman. Papa parle près du crochet. L'écharpe, au crochet, Sarah. Les mots de Sarah se cognent aux siens. Personne ne tourne la tête. Papa, le chemin ! Tu disais quelque chose, Sarah ? Le chemin d'argent. Le sourire de Sarah disparaît. L'éclat d'escargot tremble, puis tient. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne sort pas, maman. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux raconter le chemin ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. Au revoir, Sarah. Au revoir, maman. On revient te chercher. Au revoir, papa. En ce moment, Sarah entre dans la classe. La classe sent les crayons et le lait tiède. Sarah pose l'écharpe au crochet. Le tapis est un peu froid, sous les genoux. Elle s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Le chemin d'argent reste sur la vitre. La maîtresse parle près du tapis. Une affiche montre un animal lent. Sarah a une idée. Le chemin d'escargot brille, près d'elle. Je veux parler du chemin.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Francine arrive en classe avec maman. Maman dit au revoir. Francine s'assoit sur le tapis. La maîtresse pose une question. Francine a une idée. Elle lève la main. Il faut &lt;emphasis&gt;attendre&lt;/emphasis&gt;. Un camarade parle d'abord. Francine attend encore. Puis la maîtresse dit : Francine, c'est ton tour. Francine parle. Elle dit : le nuage est blanc. La maîtresse sourit. Plus tard, au coin des livres, Francine a encore une idée. Même leçon, autre lieu. Elle lève la main. Elle attend. Puis parler, c'est son tour. Elle dit : j'aime ce livre. Le soir, maman demande. Francine dit : j'ai levé la main. J'ai su attendre. Puis parler, c'était mon tour. [pause]</t>
+          <t>Un chemin d'argent court sur la vitre. Il est mince, un peu luisant. L'air sent le savon de maman. L'écharpe de laine chatouille la joue de Sarah. Elle pique un peu, maman. C'est la laine, près du cou. Le radiateur de l'entrée fait tic. Tu l'entends, Sarah ? Oui, papa. Il chante, près de nous. Sarah connaît cette entrée. Ce chemin, lui, est nouveau. Sur la vitre, un &lt;emphasis&gt;éclat d'escargot&lt;/emphasis&gt; brille. Il est petit, papa. C'est le soleil sur le chemin. Un escargot est passé ! Tu as vu le petit chemin luisant ? Il brille. Je veux le dire, maintenant ! Tes gants sont dans la poche. Tu les sens ? Oui. Ils sont chauds. Dehors, l'air est frais. La vitre est froide sous le doigt. Elle est lisse, papa. Maman tourne l'écharpe, un tour. Pas trop serré. D'accord, maman. Papa parle près du crochet. L'écharpe, au crochet, Sarah. Les mots de Sarah se cognent aux siens. Personne ne tourne la tête. Papa, le chemin ! Tu disais quelque chose, Sarah ? Le chemin d'argent. Le sourire de Sarah disparaît. L'éclat d'escargot tremble, puis tient. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne sort pas, maman. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu veux raconter le chemin ? Oui, papa. Tu vas t'asseoir sur le tapis ? D'accord, maman. Au revoir, Sarah. Au revoir, maman. On revient te chercher. Au revoir, papa. En ce moment, Sarah entre dans la classe. La classe sent les crayons et le lait tiède. Sarah pose l'écharpe au crochet. Le tapis est un peu froid, sous les genoux. Elle s'assoit près de la fenêtre. Elle pose les mains sur ses genoux. Le chemin d'argent reste sur la vitre. La maîtresse parle près du tapis. Une affiche montre un animal lent. Sarah a une idée. Le chemin d'escargot brille, près d'elle. Je veux parler du chemin. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1.12</v>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>éclat d'escargot</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,50 +1326,80 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_dire_le_chemin_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un bouton de laine pend au manteau.
-narrateur|Il tient par un seul fil, tout fin.
-narrateur|L'écharpe chatouille encore la joue de Sarah.
-narrateur|Elle sent le savon de maman.
-maman|L'écharpe, un tour.
-maman|Pas trop serré.
+          <t>narrateur|Un chemin d'argent court sur la vitre.
+narrateur|Il est mince, un peu luisant.
+narrateur|L'air sent le savon de maman.
+narrateur|L'écharpe de laine chatouille la joue de Sarah.
+enfant-f|Elle pique un peu, maman.
+maman|C'est la laine, près du cou.
+papa|Le radiateur de l'entrée fait tic.
+papa|Tu l'entends, Sarah ?
+enfant-f|Oui, papa.
+enfant-f|Il chante, près de nous.
+narrateur|Sarah connaît cette entrée.
+narrateur|Ce chemin, lui, est nouveau.
+narrateur|Sur la vitre, un éclat d'escargot brille.
+enfant-f|Il est petit, papa.
+papa|C'est le soleil sur le chemin.
+enfant-f|Un escargot est passé !
+maman|Tu as vu le petit chemin luisant ?
+enfant-f|Il brille.
+enfant-f|Je veux le dire, maintenant !
 papa|Tes gants sont dans la poche.
 papa|Tu les sens ?
 enfant-f|Oui.
-enfant-f|Ils sont tout doux.
-narrateur|Dehors, l'air est frais et calme.
-narrateur|Sur la boîte aux lettres, une traînée brillante.
-narrateur|Un escargot est passé, tout lentement.
-papa|Tu as vu le petit chemin luisant ?
-enfant-f|Il brille.
-enfant-f|Comme un fil d'argent.
-maman|Tu pourras le raconter.
-narrateur|Le chemin sent l'herbe coupée.
+enfant-f|Ils sont chauds.
+narrateur|Dehors, l'air est frais.
+narrateur|La vitre est froide sous le doigt.
+enfant-f|Elle est lisse, papa.
+narrateur|Maman tourne l'écharpe, un tour.
+maman|Pas trop serré.
+enfant-f|D'accord, maman.
+narrateur|Papa parle près du crochet.
+papa|L'écharpe, au crochet, Sarah.
+narrateur|Les mots de Sarah se cognent aux siens.
+narrateur|Personne ne tourne la tête.
+enfant-f|Papa, le chemin !
+papa|Tu disais quelque chose, Sarah ?
+enfant-f|Le chemin d'argent.
+narrateur|Le sourire de Sarah disparaît.
+narrateur|L'éclat d'escargot tremble, puis tient.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+enfant-f|Ça ne sort pas, maman.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu veux raconter le chemin ?
+enfant-f|Oui, papa.
+maman|Tu vas t'asseoir sur le tapis ?
+enfant-f|D'accord, maman.
+maman|Au revoir, Sarah.
+enfant-f|Au revoir, maman.
+papa|On revient te chercher.
+enfant-f|Au revoir, papa.
+narrateur|En ce moment, Sarah entre dans la classe.
 narrateur|La classe sent les crayons et le lait tiède.
-maman|Au revoir, Sarah.
-maman|On revient.
-enfant-f|Au revoir, maman.
-papa|Tu poses l'écharpe au crochet.
-narrateur|En ce moment, Sarah s'assoit près de la fenêtre.
+narrateur|Sarah pose l'écharpe au crochet.
+narrateur|Le tapis est un peu froid, sous les genoux.
+narrateur|Elle s'assoit près de la fenêtre.
 narrateur|Elle pose les mains sur ses genoux.
-narrateur|Une autre traînée brille un peu sur la vitre.
-maitresse|Bonjour.
-enfant-f|Bonjour.
-maitresse|Qui a vu un petit animal tout lent ?
+narrateur|Le chemin d'argent reste sur la vitre.
+narrateur|La maîtresse parle près du tapis.
+narrateur|Une affiche montre un animal lent.
 narrateur|Sarah a une idée.
-narrateur|L'escargot de la boîte aux lettres.
-narrateur|Le chemin d'argent.
-narrateur|Le mot est déjà là.
-narrateur|Elle avance un peu sur sa chaise.
-narrateur|La maîtresse range encore des crayons dans un pot.
-narrateur|Le pot fait un petit bruit de bois.</t>
+narrateur|Le chemin d'escargot brille, près d'elle.
+enfant-f|Je veux parler du chemin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>radiateur,echarpe</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1431,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah veut parler. Que fait-elle d'abord ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah veut &lt;emphasis level="moderate"&gt;parler&lt;/emphasis&gt;. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Francine veut parler. Que fait-elle d'abord ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Sarah veut &lt;emphasis&gt;parler&lt;/emphasis&gt;. Que fait-elle d'abord ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1469,18 +1499,18 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1495,34 +1525,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>parler</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1531,23 +1565,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_attend_puis_parle; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1580,17 +1614,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah lève la main. Elle attend, la main haute. Elle regarde la vitre, tout doucement. Sa main ne descend pas. Sarah, c'est toi. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la boîte aux lettres. Comme un fil d'argent. Un chemin d'argent, oui. Il allait tout lentement. Merci, Sarah. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Il y a un escargot, tout lent, sur une feuille. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est toi, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Comme celui de la boîte. Comme celui de la boîte.</t>
+          <t>Sarah ouvre la bouche trop vite. L'escargot a laissé un chemin ! Un camarade parle, près du tapis. J'ai vu un ver de terre. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Sarah attend que le silence arrive. Sur la vitre, l'éclat d'escargot brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Un escargot a laissé un chemin. Il brille sur la vitre. Sarah montre la vitre du doigt. Il est mince, comme ça. Les genoux restent sur le tapis. Plus tard, c'est le coin des livres. Un banc de bois attend. Sarah ouvre un album aux pages épaisses. Sur une page, un escargot avance. Comme sur la vitre ! Sarah a envie de le dire, d'un coup.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah lève la main. Elle attend, la main haute. Elle regarde la vitre, tout doucement. Sa main ne descend pas. Sarah, c'est toi. Tu peux parler. L'escargot a laissé un chemin. Il brille sur la boîte aux lettres. Comme un fil d'argent. Un chemin d'argent, oui. Il allait tout lentement. Merci, Sarah. Plus tard, au coin des livres, un banc de bois attend. Sarah ouvre un album aux pages épaisses. Il y a un escargot, tout lent, sur une feuille. Elle a encore une idée. Elle lève la main. Elle attend. Sarah, c'est toi, ici aussi. J'aime ce livre. Il y a un escargot, tout lent. Comme celui de la boîte. Comme celui de la boîte.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah ouvre la bouche trop vite. L'escargot a laissé un chemin ! Un camarade parle, près du tapis. J'ai vu un ver de terre. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Sarah attend que le &lt;emphasis level="moderate"&gt;silence&lt;/emphasis&gt; arrive. Sur la vitre, l'éclat d'escargot brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Un escargot a laissé un chemin. Il brille sur la vitre. Sarah montre la vitre du doigt. Il est mince, comme ça. Les genoux restent sur le tapis. Plus tard, c'est le coin des livres. Un banc de bois attend. Sarah ouvre un album aux pages épaisses. Sur une page, un escargot avance. Comme sur la vitre ! Sarah a envie de le dire, d'un coup.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Francine a levé la main. Elle a attendu. &lt;emphasis&gt;puis&lt;/emphasis&gt; parler, c'était son tour. Au tapis, puis aux livres. [pause]</t>
+          <t>Sarah ouvre la bouche trop vite. L'escargot a laissé un chemin ! Un camarade parle, près du tapis. J'ai vu un ver de terre. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme la bouche. Elle lève la main, près du tapis. Sa main reste en l'air. Le camarade finit sa phrase. Sarah attend que le &lt;emphasis&gt;silence&lt;/emphasis&gt; arrive. Sur la vitre, l'éclat d'escargot brille. Je peux dire quelque chose ? La classe tourne un peu la tête. Un escargot a laissé un chemin. Il brille sur la vitre. Sarah montre la vitre du doigt. Il est mince, comme ça. Les genoux restent sur le tapis. Plus tard, c'est le coin des livres. Un banc de bois attend. Sarah ouvre un album aux pages épaisses. Sur une page, un escargot avance. Comme sur la vitre ! Sarah a envie de le dire, d'un coup. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1637,7 +1671,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1645,10 +1679,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,7 +1705,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>puis</t>
+          <t>silence</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1685,16 +1719,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1703,10 +1737,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1719,39 +1753,43 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=soulagement_prudent; intensite=1; destinataire=enfant; sous_texte=elle_refuse_de_foncer_puis_parle; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah lève la main.
-narrateur|Elle attend, la main haute.
-narrateur|Elle regarde la vitre, tout doucement.
-narrateur|Sa main ne descend pas.
-maitresse|Sarah, c'est toi.
-maitresse|Tu peux parler.
-enfant-f|L'escargot a laissé un chemin.
-enfant-f|Il brille sur la boîte aux lettres.
-enfant-f|Comme un fil d'argent.
-maitresse|Un chemin d'argent, oui.
-enfant-f|Il allait tout lentement.
-maitresse|Merci, Sarah.
-narrateur|Plus tard, au coin des livres, un banc de bois attend.
+          <t>narrateur|Sarah ouvre la bouche trop vite.
+enfant-f|L'escargot a laissé un chemin !
+narrateur|Un camarade parle, près du tapis.
+copain|J'ai vu un ver de terre.
+narrateur|Les deux voix se mélangent.
+enfant-f|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Sarah refuse de foncer.
+narrateur|Elle referme la bouche.
+narrateur|Elle lève la main, près du tapis.
+narrateur|Sa main reste en l'air.
+narrateur|Le camarade finit sa phrase.
+narrateur|Sarah attend que le silence arrive.
+narrateur|Sur la vitre, l'éclat d'escargot brille.
+enfant-f|Je peux dire quelque chose ?
+narrateur|La classe tourne un peu la tête.
+enfant-f|Un escargot a laissé un chemin.
+enfant-f|Il brille sur la vitre.
+narrateur|Sarah montre la vitre du doigt.
+enfant-f|Il est mince, comme ça.
+narrateur|Les genoux restent sur le tapis.
+narrateur|Plus tard, c'est le coin des livres.
+narrateur|Un banc de bois attend.
 narrateur|Sarah ouvre un album aux pages épaisses.
-narrateur|Il y a un escargot, tout lent, sur une feuille.
-narrateur|Elle a encore une idée.
-narrateur|Elle lève la main.
-narrateur|Elle attend.
-maitresse|Sarah, c'est toi, ici aussi.
-enfant-f|J'aime ce livre.
-enfant-f|Il y a un escargot, tout lent.
-maitresse|Comme celui de la boîte.
-enfant-f|Comme celui de la boîte.</t>
+narrateur|Sur une page, un escargot avance.
+enfant-f|Comme sur la vitre !
+narrateur|Sarah a envie de le dire, d'un coup.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>pages</t>
+          <t>tapis,pages</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1816,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai parlé de l'escargot. Et du livre, aussi. Le chemin d'argent ? Oui. Sur la boîte aux lettres. On rentre. Le bouton tient encore, tout juste. Le soir, l'écharpe sèche près du radiateur. Sarah regarde la boîte aux lettres, par la porte. Le chemin est encore un peu là. Un peu, oui. Demain, il sera peut-être parti. Sarah touche le fil du bouton. On le recoud tout à l'heure. Le livre aussi avait un escargot. Tout lent, comme le vrai.</t>
+          <t>Sarah veut tout dire, d'un coup. Elle tire l'album trop vite. Les pages se collent un peu. L'album glisse vers le banc. Ça tombe ! Sarah veut foncer, d'un coup. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle pose l'album à plat. Elle écoute le coin des livres. Un autre enfant feuillette, plus loin. Sarah attend le silence, un instant. Je peux dire quelque chose ? Il y a un escargot, dans le livre. La page sent le papier épais. Le soir, la porte s'ouvre. Te voilà, Sarah. L'écharpe sent le savon. Sarah pose le cartable contre le mur. J'ai parlé du chemin. Après le ver de terre. Merci, Sarah. Papa a entendu toute la phrase. Tu as soif ? Un peu, maman. Le ventre de Sarah se desserre. L'écharpe, tu la vois ? Oui, papa. Le bois du crochet tient la laine.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Sarah range son cartable. L'écharpe de laine est encore au crochet. La porte s'ouvre. Tu as passé un bon moment ? J'ai parlé de l'escargot. Et du livre, aussi. Le chemin d'argent ? Oui. Sur la boîte aux lettres. On rentre. Le bouton tient encore, tout juste. Le soir, l'écharpe sèche près du radiateur. Sarah regarde la boîte aux lettres, par la porte. Le chemin est encore un peu là. Un peu, oui. Demain, il sera peut-être parti. Sarah touche le fil du bouton. On le recoud tout à l'heure. Le livre aussi avait un escargot. Tout lent, comme le vrai.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah veut tout dire, d'un coup. Elle tire l'&lt;emphasis level="moderate"&gt;album&lt;/emphasis&gt; trop vite. Les pages se collent un peu. L'album glisse vers le banc. Ça tombe ! Sarah veut foncer, d'un coup. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle pose l'album à plat. Elle écoute le coin des livres. Un autre enfant feuillette, plus loin. Sarah attend le silence, un instant. Je peux dire quelque chose ? Il y a un escargot, dans le livre. La page sent le papier épais. Le soir, la porte s'ouvre. Te voilà, Sarah. L'écharpe sent le savon. Sarah pose le cartable contre le mur. J'ai parlé du chemin. Après le ver de terre. Merci, Sarah. Papa a entendu toute la phrase. Tu as soif ? Un peu, maman. Le ventre de Sarah se desserre. L'écharpe, tu la vois ? Oui, papa. Le bois du crochet tient la laine.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Francine range son cartable. Maman l'attend à la porte. [pause]</t>
+          <t>Sarah veut tout dire, d'un coup. Elle tire l'&lt;emphasis&gt;album&lt;/emphasis&gt; trop vite. Les pages se collent un peu. L'album glisse vers le banc. Ça tombe ! Sarah veut foncer, d'un coup. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle pose l'album à plat. Elle écoute le coin des livres. Un autre enfant feuillette, plus loin. Sarah attend le silence, un instant. Je peux dire quelque chose ? Il y a un escargot, dans le livre. La page sent le papier épais. Le soir, la porte s'ouvre. Te voilà, Sarah. L'écharpe sent le savon. Sarah pose le cartable contre le mur. J'ai parlé du chemin. Après le ver de terre. Merci, Sarah. Papa a entendu toute la phrase. Tu as soif ? Un peu, maman. Le ventre de Sarah se desserre. L'écharpe, tu la vois ? Oui, papa. Le bois du crochet tient la laine. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1835,7 +1873,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1881,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1867,28 +1905,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>album</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1897,10 +1939,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1911,34 +1953,49 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_l_eclat_tient; tempo=naturel; sourire=franc; respiration=relâchée</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Sarah range son cartable.
-narrateur|L'écharpe de laine est encore au crochet.
-narrateur|La porte s'ouvre.
-maman|Tu as passé un bon moment ?
-enfant-f|J'ai parlé de l'escargot.
-enfant-f|Et du livre, aussi.
-papa|Le chemin d'argent ?
-enfant-f|Oui.
-enfant-f|Sur la boîte aux lettres.
-maman|On rentre.
-papa|Le bouton tient encore, tout juste.
-narrateur|Le soir, l'écharpe sèche près du radiateur.
-narrateur|Sarah regarde la boîte aux lettres, par la porte.
-enfant-f|Le chemin est encore un peu là.
-maman|Un peu, oui.
-papa|Demain, il sera peut-être parti.
-narrateur|Sarah touche le fil du bouton.
-maman|On le recoud tout à l'heure.
-enfant-f|Le livre aussi avait un escargot.
-papa|Tout lent, comme le vrai.</t>
+          <t>narrateur|Sarah veut tout dire, d'un coup.
+narrateur|Elle tire l'album trop vite.
+narrateur|Les pages se collent un peu.
+narrateur|L'album glisse vers le banc.
+enfant-f|Ça tombe !
+narrateur|Sarah veut foncer, d'un coup.
+narrateur|Sarah refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Elle pose l'album à plat.
+narrateur|Elle écoute le coin des livres.
+narrateur|Un autre enfant feuillette, plus loin.
+narrateur|Sarah attend le silence, un instant.
+enfant-f|Je peux dire quelque chose ?
+enfant-f|Il y a un escargot, dans le livre.
+narrateur|La page sent le papier épais.
+narrateur|Le soir, la porte s'ouvre.
+maman|Te voilà, Sarah.
+papa|L'écharpe sent le savon.
+narrateur|Sarah pose le cartable contre le mur.
+enfant-f|J'ai parlé du chemin.
+enfant-f|Après le ver de terre.
+papa|Merci, Sarah.
+narrateur|Papa a entendu toute la phrase.
+maman|Tu as soif ?
+enfant-f|Un peu, maman.
+narrateur|Le ventre de Sarah se desserre.
+papa|L'écharpe, tu la vois ?
+enfant-f|Oui, papa.
+narrateur|Le bois du crochet tient la laine.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>pas</t>
+          <t>pages,porte</t>
         </is>
       </c>
     </row>
@@ -1965,17 +2022,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande.</t>
+          <t>Ils s'arrêtent devant la vitre. Le chemin d'argent est plus sec. L'éclat est là, papa. Tu le vois sur le chemin ? Oui, papa. On est bien, ici. Plus tard, l'écharpe sèche près du radiateur. Ça sent le savon, un peu. Comme ce matin. Tu souffles ? Oui, papa. Sarah souffle. Le ventre est large, à sa place. On m'a entendue. On t'a entendue, Sarah. Oui, maman. Sarah pose la joue près de l'écharpe. La laine est sèche, un peu rêche. C'est chaud. Dehors, la vitre garde le chemin. L'éclat d'escargot tient sur la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le bouton de laine ne pend plus. Le chemin était d'argent. Bonne soirée, ma grande.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'arrêtent devant la vitre. Le chemin d'argent est plus sec. L'éclat est là, papa. Tu le vois sur le chemin ? Oui, papa. On est bien, ici. Plus tard, l'écharpe sèche près du radiateur. Ça sent le savon, un peu. Comme ce matin. Tu souffles ? Oui, papa. Sarah souffle. Le ventre est large, à sa place. On m'a entendue. On t'a entendue, Sarah. Oui, maman. Sarah pose la joue près de l'écharpe. La laine est sèche, un peu rêche. C'est chaud. Dehors, la vitre garde le chemin. L'&lt;emphasis level="moderate"&gt;éclat d'escargot&lt;/emphasis&gt; tient sur la vitre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'arrêtent devant la vitre. Le chemin d'argent est plus sec. L'éclat est là, papa. Tu le vois sur le chemin ? Oui, papa. On est bien, ici. Plus tard, l'écharpe sèche près du radiateur. Ça sent le savon, un peu. Comme ce matin. Tu souffles ? Oui, papa. Sarah souffle. Le ventre est large, à sa place. On m'a entendue. On t'a entendue, Sarah. Oui, maman. Sarah pose la joue près de l'écharpe. La laine est sèche, un peu rêche. C'est chaud. Dehors, la vitre garde le chemin. L'&lt;emphasis&gt;éclat d'escargot&lt;/emphasis&gt; tient sur la vitre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2022,18 +2079,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2042,12 +2099,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2056,17 +2113,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat d'escargot</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2075,11 +2136,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2088,26 +2149,53 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_tient_sur_la_vitre; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le bouton de laine ne pend plus.
-papa|Le chemin était d'argent.
-maman|Bonne soirée, ma grande.</t>
+          <t>narrateur|Ils s'arrêtent devant la vitre.
+narrateur|Le chemin d'argent est plus sec.
+enfant-f|L'éclat est là, papa.
+papa|Tu le vois sur le chemin ?
+enfant-f|Oui, papa.
+maman|On est bien, ici.
+narrateur|Plus tard, l'écharpe sèche près du radiateur.
+narrateur|Ça sent le savon, un peu.
+enfant-f|Comme ce matin.
+papa|Tu souffles ?
+enfant-f|Oui, papa.
+narrateur|Sarah souffle.
+narrateur|Le ventre est large, à sa place.
+enfant-f|On m'a entendue.
+maman|On t'a entendue, Sarah.
+enfant-f|Oui, maman.
+narrateur|Sarah pose la joue près de l'écharpe.
+narrateur|La laine est sèche, un peu rêche.
+enfant-f|C'est chaud.
+narrateur|Dehors, la vitre garde le chemin.
+narrateur|L'éclat d'escargot tient sur la vitre.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>radiateur,vitre</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2301,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
